--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD4D69C9-9D3D-452C-8F50-40DF037A8C2A}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F01B0B-B594-4E00-A227-B9FE44205342}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
   <si>
     <t>TaskID</t>
   </si>
@@ -51,58 +62,68 @@
     <t>done</t>
   </si>
   <si>
-    <t>Een Klasse Passagier maken met nodige functies om een object Passagier te maken met nodige informatie</t>
-  </si>
-  <si>
-    <t>•	Elke passagier moet een volledige naam, een rijksregisternummer en een geboorte datum bevatten
-•	Ongeldige invoer worden geweigerd met een foutmelding</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>Een Reis klasse maken die een object Tijdstip en Traject meeneemt. 
-Een klasse Personeelslid aanmaken waarvan de volgende klasse een lijst van certificaties zal erfen. 
-Klasse Bestuurder, Steward en BagagePersoneel aanmaken met nodige functies om nodige informatie te behouden.</t>
-  </si>
-  <si>
-    <t>•	Een reis heeft 1 vertrekpunt en 1 aankomstpunt
-•	Een reis heeft 1 vertrek uur en 1 aankomst uur
-•	Een reis heeft minstens 1 bestuurder en 3 stewards
-•	Een personeelslid moet minstens 1 certificatie hebben</t>
-  </si>
-  <si>
-    <t>Een enumeratie TypeLocomotief maken. Elke type bevat een aantal wagon, deze aantal zal het maximum aantal plaatsen bepalen. 
-Een klasse Wagon aanmaken waar een lijst staat dat gevuld kan worden met passagieren. 
-Bij elke nieuwe trein wordt de lijst van wagons volledig gevuld tot het aantal maximale wagons dat werd vastegestelt door het type locomotief.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Een trein bestaat uit 1 type locomotief en meerdere wagons (aantal wagons wordt dan bepaalt door het type locomotief)
-•	Een reis bestaat uit maximaal 1 trein
-•	Er moet minimaal 1 reis vooraf gemaakt worden
+    <t>Als een user die de website bezoekt, wil ik mijn gebruikersvoorkeuren en bepaalde locaties kunnen opslaan, waarbij deze favoriete collecties en gebruikersvoorkeuren worden bewaard tussen verschillende sessies.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om deze website op verschillende devices te bezoeken met verschillende dimensies met een aangename en duidelijke interface, zodat ik deze website overal en op alle devices kan bezoeken.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik een lijst van alle historische locaties in Brussel in een tabel met minimum 6 kolommen van informatie, zodat ik me kan informeren over alle beschikbare historische locaties in Brussel.</t>
+  </si>
+  <si>
+    <t>Bij het opstarten van het website wordt een functie fetchData() opgeroept om de API aan te spreken, en via een functie updateMainList() de effectieve lijst van locaties te maken / aan te passen.</t>
+  </si>
+  <si>
+    <t>De url moet effectief naar de API die de dataset van de historische locaties bevat verwijzen zonder fouten.</t>
+  </si>
+  <si>
+    <t>Bepaalde items (bijvoorbeeld: favoriete locaties, gekozen taal, …) in de localStorage van de user steken om later de website aan te passen volgens zijn voorkeuren.
+De taal van de user wordt gekozen door twee buttons op de main pagina, die de key (taal) aanpast in de localStorage. Vervolgens wordt er met checkLanguage() (bij elk verandering van de taal EN wanneer de pagina laad) de hele pagina aangepast volgens de taal van de user.
+Een user kan door een klein knopje een locatie als favoriet kiezen, en kan deze zien in het menu van favoriete locaties. Een favoriete locatie wordt bijgehouden in een array, onder de key (favorites) in de localStorage van de user.</t>
+  </si>
+  <si>
+    <t>Elk user dat voor het eerst de website bezoekt moet een default waarde krijgen voor elke mogelijke key in de localStorage, bijvoorbeeld "nl" bij "taal".</t>
+  </si>
+  <si>
+    <t>In de CSS file verschillende media querries aanmaken die ervoor zorgen dat de website op elke mogelijke device bruikbaar is.</t>
+  </si>
+  <si>
+    <t>De website moet zich aanpassen volgens deze verschillende schermgroottes:
+…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst van historische locaties in Brussel te filtreren (op type, locatie, etc…), zodat ik mijn lijst kan beperken tot de gemeente dat ik nodig heb. </t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om een specifieke locatie op te zoeken, zodat ik op een snelle manier een locatie kan vinden.</t>
+  </si>
+  <si>
+    <t>Door op de knop "search" te drukken, opent een cover, waarin alle locaties worden opgelijst. Een user kan dan intypen in het balk bovenaan om een specifieke locatie op naam op te zoeken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
+Sorteermethode...
 </t>
   </si>
   <si>
-    <t>Een klasse Ticket maken die een object Passagier, object Reis en een waarde uit een enumeratie Klasse bevat</t>
-  </si>
-  <si>
-    <t>•	Er moet miniaal 1 passagier vooraf geregistreerd worden
-•	Er moet minimaal 1 reis vooraf gemaakt worden
-•	Een ticket bevat 1 object Reis, 1 object Passagier en 1 waarde uit enum Klasse
-•	Een passagier moet op 1 wagon geregistreerd worden
-•	Bij elke reis hoort er een maximale aantal plaatsen, dat wordt bepaalt door de type locomotief. Bij een volle trein wordt het verkopen van een ticket voor deze reis geweigerd</t>
-  </si>
-  <si>
-    <t>Als een user die de website bezoekt, wil ik een lijst van alle historische locaties in Brussel in een tabel met minimum 6 kolommen van informatie, zodat ik me kan informeren over alle beschikbare historische locaties in Brussel.E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst van historische locaties in Brussel te filtreren (op type, locatie, etc…) en deze te sorteren en een specifieke locatie op te zoeken op basis van zijn naam, zodat ik snel en efficiënt een bepaalde locatie kan vinden. </t>
-  </si>
-  <si>
-    <t>Als een user die de website bezoekt, wil ik mijn gebruikersvoorkeuren en bepaalde locaties kunnen opslaan, waarbij deze favoriete collecties en gebruikersvoorkeuren worden bewaard tussen verschillende sessies.</t>
-  </si>
-  <si>
-    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om deze website op verschillende devices te bezoeken met verschillende dimensies met een aangename en duidelijke interface, zodat ik deze website overal en op alle devices kan bezoeken.</t>
+    <t>Om een locatie op te zoeken, moet de user het zoeken op basis van de naam van de locatie. Minstens één locatie met deze naam moet bestaan om een lijst te krijgen, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanneer een post-code wordt ingevoerd in de input voor de post-code, worden alle elementen met die zelfde post-code samengenomen en getoond in de lijst. 
+</t>
+  </si>
+  <si>
+    <t>Sorteermethode…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
+</t>
   </si>
 </sst>
 </file>
@@ -456,12 +477,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H7"/>
+  <dimension ref="B2:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="42.28515625" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="7" width="74.5703125" customWidth="1"/>
+    <col min="5" max="5" width="62.140625" customWidth="1"/>
+    <col min="6" max="6" width="97" customWidth="1"/>
+    <col min="7" max="7" width="110.7109375" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,7 +509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -499,16 +520,16 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="246" customHeight="1" x14ac:dyDescent="0.25">
@@ -525,16 +546,16 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="246" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -548,16 +569,14 @@
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="2:8" ht="246" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -568,28 +587,73 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F01B0B-B594-4E00-A227-B9FE44205342}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24067FB8-9E2F-4F97-8E28-D3F664A41BA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>TaskID</t>
   </si>
@@ -65,9 +65,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Als een user die de website bezoekt, wil ik mijn gebruikersvoorkeuren en bepaalde locaties kunnen opslaan, waarbij deze favoriete collecties en gebruikersvoorkeuren worden bewaard tussen verschillende sessies.</t>
-  </si>
-  <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om deze website op verschillende devices te bezoeken met verschillende dimensies met een aangename en duidelijke interface, zodat ik deze website overal en op alle devices kan bezoeken.</t>
   </si>
   <si>
@@ -78,11 +75,6 @@
   </si>
   <si>
     <t>De url moet effectief naar de API die de dataset van de historische locaties bevat verwijzen zonder fouten.</t>
-  </si>
-  <si>
-    <t>Bepaalde items (bijvoorbeeld: favoriete locaties, gekozen taal, …) in de localStorage van de user steken om later de website aan te passen volgens zijn voorkeuren.
-De taal van de user wordt gekozen door twee buttons op de main pagina, die de key (taal) aanpast in de localStorage. Vervolgens wordt er met checkLanguage() (bij elk verandering van de taal EN wanneer de pagina laad) de hele pagina aangepast volgens de taal van de user.
-Een user kan door een klein knopje een locatie als favoriet kiezen, en kan deze zien in het menu van favoriete locaties. Een favoriete locatie wordt bijgehouden in een array, onder de key (favorites) in de localStorage van de user.</t>
   </si>
   <si>
     <t>Elk user dat voor het eerst de website bezoekt moet een default waarde krijgen voor elke mogelijke key in de localStorage, bijvoorbeeld "nl" bij "taal".</t>
@@ -104,11 +96,6 @@
     <t>Door op de knop "search" te drukken, opent een cover, waarin alle locaties worden opgelijst. Een user kan dan intypen in het balk bovenaan om een specifieke locatie op naam op te zoeken.</t>
   </si>
   <si>
-    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
-Sorteermethode...
-</t>
-  </si>
-  <si>
     <t>Om een locatie op te zoeken, moet de user het zoeken op basis van de naam van de locatie. Minstens één locatie met deze naam moet bestaan om een lijst te krijgen, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.</t>
   </si>
   <si>
@@ -124,6 +111,18 @@
   <si>
     <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
 </t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
+  </si>
+  <si>
+    <t>Twee buttons aanmaken om de taal van de user te switchen. Wanneer een button gedrukt werd, herlaad de hele website volgens de gekoze taal en wordt de taal opgeslagen in de localStorage van de user.</t>
+  </si>
+  <si>
+    <t>Een user kan door een klein knopje een locatie als favoriet kiezen, en kan deze zien in het menu van favoriete locaties. Een favoriete locatie wordt bijgehouden in een array, onder de key (favorites) in de localStorage van de user.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik bepaalde locaties als favoriet kunnen opslaan, waarbij deze locaties wordt bijgehouden tussen mijn sessies, zodat ik snel mijn locaties kan terug vinden.</t>
   </si>
 </sst>
 </file>
@@ -212,6 +211,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H9"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="62.140625" customWidth="1"/>
@@ -520,13 +523,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -543,13 +546,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -566,13 +569,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="H5" s="2"/>
     </row>
@@ -587,13 +590,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -608,49 +611,62 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+    <row r="8" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+    <row r="10" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24067FB8-9E2F-4F97-8E28-D3F664A41BA6}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69861217-FEA4-43DE-8098-C75E281C0B4A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>TaskID</t>
   </si>
@@ -71,58 +71,105 @@
     <t>Als een user die de website bezoekt, wil ik een lijst van alle historische locaties in Brussel in een tabel met minimum 6 kolommen van informatie, zodat ik me kan informeren over alle beschikbare historische locaties in Brussel.</t>
   </si>
   <si>
-    <t>Bij het opstarten van het website wordt een functie fetchData() opgeroept om de API aan te spreken, en via een functie updateMainList() de effectieve lijst van locaties te maken / aan te passen.</t>
-  </si>
-  <si>
-    <t>De url moet effectief naar de API die de dataset van de historische locaties bevat verwijzen zonder fouten.</t>
-  </si>
-  <si>
-    <t>Elk user dat voor het eerst de website bezoekt moet een default waarde krijgen voor elke mogelijke key in de localStorage, bijvoorbeeld "nl" bij "taal".</t>
-  </si>
-  <si>
     <t>In de CSS file verschillende media querries aanmaken die ervoor zorgen dat de website op elke mogelijke device bruikbaar is.</t>
   </si>
   <si>
-    <t>De website moet zich aanpassen volgens deze verschillende schermgroottes:
-…</t>
-  </si>
-  <si>
     <t xml:space="preserve">Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst van historische locaties in Brussel te filtreren (op type, locatie, etc…), zodat ik mijn lijst kan beperken tot de gemeente dat ik nodig heb. </t>
   </si>
   <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om een specifieke locatie op te zoeken, zodat ik op een snelle manier een locatie kan vinden.</t>
   </si>
   <si>
-    <t>Door op de knop "search" te drukken, opent een cover, waarin alle locaties worden opgelijst. Een user kan dan intypen in het balk bovenaan om een specifieke locatie op naam op te zoeken.</t>
-  </si>
-  <si>
-    <t>Om een locatie op te zoeken, moet de user het zoeken op basis van de naam van de locatie. Minstens één locatie met deze naam moet bestaan om een lijst te krijgen, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.</t>
-  </si>
-  <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
   </si>
   <si>
-    <t xml:space="preserve">Wanneer een post-code wordt ingevoerd in de input voor de post-code, worden alle elementen met die zelfde post-code samengenomen en getoond in de lijst. 
+    <t>Sorteermethode…</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik bepaalde locaties als favoriet kunnen opslaan, waarbij deze locatie wordt bijgehouden tussen mijn sessies, zodat ik snel mijn locaties kan terug vinden.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik een duidelijke een aantrekkelijke UI, waarvan de button duidelijk aantonen wat hun functies zijn, zodat ik de website op een efficiënte manier kan gebruiken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De website toont een lijst van historische locaties in een tabel
+De tabel bevat minstens 6 kolommen met relevante informatie
+De data wordt correct opgehaald via de API
+Bij een fout in de fetch wordt een foutmelding getoond
 </t>
   </si>
   <si>
-    <t>Sorteermethode…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
+    <t xml:space="preserve">De gebruiker kan filteren op minstens één criterium (bv. type of locatie)
+De lijst past zich aan wanneer de user op de filtreer button klikt, op basis van de gekozen filters
+Enkel overeenkomende resultaten worden weergegeven
+Bij geen resultaten wordt een duidelijke melding getoond
+De gebruiker kan filters resetten, wat alle locaties opnieuw toont
 </t>
   </si>
   <si>
-    <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
-  </si>
-  <si>
-    <t>Twee buttons aanmaken om de taal van de user te switchen. Wanneer een button gedrukt werd, herlaad de hele website volgens de gekoze taal en wordt de taal opgeslagen in de localStorage van de user.</t>
-  </si>
-  <si>
-    <t>Een user kan door een klein knopje een locatie als favoriet kiezen, en kan deze zien in het menu van favoriete locaties. Een favoriete locatie wordt bijgehouden in een array, onder de key (favorites) in de localStorage van de user.</t>
-  </si>
-  <si>
-    <t>Als een user die de website bezoekt, wil ik bepaalde locaties als favoriet kunnen opslaan, waarbij deze locaties wordt bijgehouden tussen mijn sessies, zodat ik snel mijn locaties kan terug vinden.</t>
+    <t>De gebruiker kan zoeken op naam van een locatie
+De lijst wordt live aangepast tijdens het typen
+Bij een lege zoekopdracht wordt de volledige lijst getoond
+Bij geen resultaten wordt een melding weergegeven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De gebruiker kan de lijst sorteren volgens minstens één criterium
+De sortering wordt correct toegepast op de volledige lijst
+De lijst wordt visueel aangepast na sortering
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De gebruiker kan locaties toevoegen aan favorieten
+Favorieten worden opgeslagen in LocalStorage
+Favorieten blijven bewaard tussen sessies
+Dubbele favorieten worden niet toegestaan
+</t>
+  </si>
+  <si>
+    <t>De gebruiker kan een taalvoorkeur selecteren
+De gekozen taal wordt opgeslagen in LocalStorage
+De taal wordt automatisch toegepast bij herladen van de website
+Een standaardtaal wordt ingesteld bij eerste bezoek</t>
+  </si>
+  <si>
+    <t>De website werkt op verschillende schermgroottes
+De layout past zich automatisch aan (desktop, tablet, mobiel)
+Elementen blijven leesbaar en bruikbaar op alle devices
+Geen functionaliteit gaat verloren bij kleinere schermen</t>
+  </si>
+  <si>
+    <t>De interface is overzichtelijk en consistent
+Knoppen zijn duidelijk herkenbaar en begrijpelijk
+Interactieve elementen geven visuele feedback
+Navigatie is intuïtief en gebruiksvriendelijk</t>
+  </si>
+  <si>
+    <t>Maak een functie fetchData met als parameters withAllLanguage om eerst een array te maken met alle mogelijke locaties, dan kan fetchData zonder parameters gebruikt worden om per taal de locaties te tonen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak een filtreer button waaraan we een EventListener toevoegen
+Wanneer die button geklikt wordt, neemt het de value van de input voor de post code en past de main list eraan toe.
+Er moet ook gechekt worden of de input effectief een belgische post code kan zijn, dus maximaal en minimaal 4 digits
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak een search button en voeg er een EventListeren toe. Wanneer de button geklikt wordt, wordt er een  nieuwe cover opnieuw gemaakt.
+In de cover wordt een nieuwe lijst aangemaakt met alle mogelijke locaties, waarvan de taal veranderd wegens een check op voorhand op de localStorage.
+Een balk wordt toegevoegd, waaraan een EventListener elke input detecteert, en bij elke input wordt er gechekt of er locaties zijn die corresponderen met wat er in de balk werd ingevoerd.  </t>
+  </si>
+  <si>
+    <t>Voor elke kaart, voeg een SVG die de ID van de locatie overneemt en een EventListener heeft. Als de SVG geklikt wordt, wordt er met .find() een relatie gezocht tussen de ID van de SVG en die in de eerste array van locaties dat we maken. Dit zal ervoor zorgen dat we de object kunnen nemen van de locatie, en zo de data op een efficiente manier kan gebruiken om die in de array van favoriete locaties pushen in de localStorage van de user.
+Via een knop kan de user een menu openen dat al zijn favoriete locaties oplijst, en kan deze ook verwijderen van zijn lijst.</t>
+  </si>
+  <si>
+    <t>Twee buttons aanmaken om de taal van de user te switchen. Wanneer een button gedrukt werd, herlaad de hele website volgens de gekoze taal en wordt de taal opgeslagen in de localStorage van de user.
+Bij het opladen van de website wordt er een check gedaan om de taal van de website aan te passen.</t>
+  </si>
+  <si>
+    <t>Duidelijke icoontjes en tekst gebruiken om ervoor te zorgen dat de website duidelijke en gebruikersvriendelijk is.</t>
   </si>
 </sst>
 </file>
@@ -483,9 +530,9 @@
   <dimension ref="B2:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="62.140625" customWidth="1"/>
-    <col min="6" max="6" width="97" customWidth="1"/>
-    <col min="7" max="7" width="110.7109375" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" customWidth="1"/>
+    <col min="7" max="7" width="64" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -526,10 +573,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -546,13 +593,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -569,15 +616,17 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="2:8" ht="246" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
@@ -590,19 +639,21 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -611,34 +662,44 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -650,23 +711,37 @@
         <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69861217-FEA4-43DE-8098-C75E281C0B4A}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FB376B-060F-42BD-B2E3-6F0C548E8E1C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>TaskID</t>
   </si>
@@ -171,12 +171,15 @@
   <si>
     <t>Duidelijke icoontjes en tekst gebruiken om ervoor te zorgen dat de website duidelijke en gebruikersvriendelijk is.</t>
   </si>
+  <si>
+    <t>Groepsleden: Lilian Levano, Bilal Benhammou</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +197,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -235,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -243,6 +254,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H10"/>
+  <dimension ref="B1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="44.85546875" customWidth="1"/>
@@ -536,6 +548,11 @@
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:8" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="2" spans="2:8" ht="63" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25F01B0B-B594-4E00-A227-B9FE44205342}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FB376B-060F-42BD-B2E3-6F0C548E8E1C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>TaskID</t>
   </si>
@@ -65,72 +65,121 @@
     <t>High</t>
   </si>
   <si>
-    <t>Als een user die de website bezoekt, wil ik mijn gebruikersvoorkeuren en bepaalde locaties kunnen opslaan, waarbij deze favoriete collecties en gebruikersvoorkeuren worden bewaard tussen verschillende sessies.</t>
-  </si>
-  <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om deze website op verschillende devices te bezoeken met verschillende dimensies met een aangename en duidelijke interface, zodat ik deze website overal en op alle devices kan bezoeken.</t>
   </si>
   <si>
     <t>Als een user die de website bezoekt, wil ik een lijst van alle historische locaties in Brussel in een tabel met minimum 6 kolommen van informatie, zodat ik me kan informeren over alle beschikbare historische locaties in Brussel.</t>
   </si>
   <si>
-    <t>Bij het opstarten van het website wordt een functie fetchData() opgeroept om de API aan te spreken, en via een functie updateMainList() de effectieve lijst van locaties te maken / aan te passen.</t>
-  </si>
-  <si>
-    <t>De url moet effectief naar de API die de dataset van de historische locaties bevat verwijzen zonder fouten.</t>
-  </si>
-  <si>
-    <t>Bepaalde items (bijvoorbeeld: favoriete locaties, gekozen taal, …) in de localStorage van de user steken om later de website aan te passen volgens zijn voorkeuren.
-De taal van de user wordt gekozen door twee buttons op de main pagina, die de key (taal) aanpast in de localStorage. Vervolgens wordt er met checkLanguage() (bij elk verandering van de taal EN wanneer de pagina laad) de hele pagina aangepast volgens de taal van de user.
-Een user kan door een klein knopje een locatie als favoriet kiezen, en kan deze zien in het menu van favoriete locaties. Een favoriete locatie wordt bijgehouden in een array, onder de key (favorites) in de localStorage van de user.</t>
-  </si>
-  <si>
-    <t>Elk user dat voor het eerst de website bezoekt moet een default waarde krijgen voor elke mogelijke key in de localStorage, bijvoorbeeld "nl" bij "taal".</t>
-  </si>
-  <si>
     <t>In de CSS file verschillende media querries aanmaken die ervoor zorgen dat de website op elke mogelijke device bruikbaar is.</t>
   </si>
   <si>
-    <t>De website moet zich aanpassen volgens deze verschillende schermgroottes:
-…</t>
-  </si>
-  <si>
     <t xml:space="preserve">Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst van historische locaties in Brussel te filtreren (op type, locatie, etc…), zodat ik mijn lijst kan beperken tot de gemeente dat ik nodig heb. </t>
   </si>
   <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om een specifieke locatie op te zoeken, zodat ik op een snelle manier een locatie kan vinden.</t>
   </si>
   <si>
-    <t>Door op de knop "search" te drukken, opent een cover, waarin alle locaties worden opgelijst. Een user kan dan intypen in het balk bovenaan om een specifieke locatie op naam op te zoeken.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
-Sorteermethode...
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
+  </si>
+  <si>
+    <t>Sorteermethode…</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik bepaalde locaties als favoriet kunnen opslaan, waarbij deze locatie wordt bijgehouden tussen mijn sessies, zodat ik snel mijn locaties kan terug vinden.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik een duidelijke een aantrekkelijke UI, waarvan de button duidelijk aantonen wat hun functies zijn, zodat ik de website op een efficiënte manier kan gebruiken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De website toont een lijst van historische locaties in een tabel
+De tabel bevat minstens 6 kolommen met relevante informatie
+De data wordt correct opgehaald via de API
+Bij een fout in de fetch wordt een foutmelding getoond
 </t>
   </si>
   <si>
-    <t>Om een locatie op te zoeken, moet de user het zoeken op basis van de naam van de locatie. Minstens één locatie met deze naam moet bestaan om een lijst te krijgen, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.</t>
-  </si>
-  <si>
-    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wanneer een post-code wordt ingevoerd in de input voor de post-code, worden alle elementen met die zelfde post-code samengenomen en getoond in de lijst. 
+    <t xml:space="preserve">De gebruiker kan filteren op minstens één criterium (bv. type of locatie)
+De lijst past zich aan wanneer de user op de filtreer button klikt, op basis van de gekozen filters
+Enkel overeenkomende resultaten worden weergegeven
+Bij geen resultaten wordt een duidelijke melding getoond
+De gebruiker kan filters resetten, wat alle locaties opnieuw toont
 </t>
   </si>
   <si>
-    <t>Sorteermethode…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Om te filtreren moet de user effectief een post-code, een nummer dus, invoeren. Minstens één locatie met die post-code moet bestaan om effectief een lijst te zien, anders wordt een bericht getoond die hem waarschuwt dat er geen locatie die corresponderen.
+    <t>De gebruiker kan zoeken op naam van een locatie
+De lijst wordt live aangepast tijdens het typen
+Bij een lege zoekopdracht wordt de volledige lijst getoond
+Bij geen resultaten wordt een melding weergegeven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De gebruiker kan de lijst sorteren volgens minstens één criterium
+De sortering wordt correct toegepast op de volledige lijst
+De lijst wordt visueel aangepast na sortering
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De gebruiker kan locaties toevoegen aan favorieten
+Favorieten worden opgeslagen in LocalStorage
+Favorieten blijven bewaard tussen sessies
+Dubbele favorieten worden niet toegestaan
+</t>
+  </si>
+  <si>
+    <t>De gebruiker kan een taalvoorkeur selecteren
+De gekozen taal wordt opgeslagen in LocalStorage
+De taal wordt automatisch toegepast bij herladen van de website
+Een standaardtaal wordt ingesteld bij eerste bezoek</t>
+  </si>
+  <si>
+    <t>De website werkt op verschillende schermgroottes
+De layout past zich automatisch aan (desktop, tablet, mobiel)
+Elementen blijven leesbaar en bruikbaar op alle devices
+Geen functionaliteit gaat verloren bij kleinere schermen</t>
+  </si>
+  <si>
+    <t>De interface is overzichtelijk en consistent
+Knoppen zijn duidelijk herkenbaar en begrijpelijk
+Interactieve elementen geven visuele feedback
+Navigatie is intuïtief en gebruiksvriendelijk</t>
+  </si>
+  <si>
+    <t>Maak een functie fetchData met als parameters withAllLanguage om eerst een array te maken met alle mogelijke locaties, dan kan fetchData zonder parameters gebruikt worden om per taal de locaties te tonen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak een filtreer button waaraan we een EventListener toevoegen
+Wanneer die button geklikt wordt, neemt het de value van de input voor de post code en past de main list eraan toe.
+Er moet ook gechekt worden of de input effectief een belgische post code kan zijn, dus maximaal en minimaal 4 digits
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak een search button en voeg er een EventListeren toe. Wanneer de button geklikt wordt, wordt er een  nieuwe cover opnieuw gemaakt.
+In de cover wordt een nieuwe lijst aangemaakt met alle mogelijke locaties, waarvan de taal veranderd wegens een check op voorhand op de localStorage.
+Een balk wordt toegevoegd, waaraan een EventListener elke input detecteert, en bij elke input wordt er gechekt of er locaties zijn die corresponderen met wat er in de balk werd ingevoerd.  </t>
+  </si>
+  <si>
+    <t>Voor elke kaart, voeg een SVG die de ID van de locatie overneemt en een EventListener heeft. Als de SVG geklikt wordt, wordt er met .find() een relatie gezocht tussen de ID van de SVG en die in de eerste array van locaties dat we maken. Dit zal ervoor zorgen dat we de object kunnen nemen van de locatie, en zo de data op een efficiente manier kan gebruiken om die in de array van favoriete locaties pushen in de localStorage van de user.
+Via een knop kan de user een menu openen dat al zijn favoriete locaties oplijst, en kan deze ook verwijderen van zijn lijst.</t>
+  </si>
+  <si>
+    <t>Twee buttons aanmaken om de taal van de user te switchen. Wanneer een button gedrukt werd, herlaad de hele website volgens de gekoze taal en wordt de taal opgeslagen in de localStorage van de user.
+Bij het opladen van de website wordt er een check gedaan om de taal van de website aan te passen.</t>
+  </si>
+  <si>
+    <t>Duidelijke icoontjes en tekst gebruiken om ervoor te zorgen dat de website duidelijke en gebruikersvriendelijk is.</t>
+  </si>
+  <si>
+    <t>Groepsleden: Lilian Levano, Bilal Benhammou</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +197,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -189,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -197,6 +254,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -212,6 +270,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,15 +539,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H9"/>
+  <dimension ref="B1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="62.140625" customWidth="1"/>
-    <col min="6" max="6" width="97" customWidth="1"/>
-    <col min="7" max="7" width="110.7109375" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" customWidth="1"/>
+    <col min="7" max="7" width="64" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:8" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="2" spans="2:8" ht="63" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -520,13 +587,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -543,13 +610,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -566,15 +633,17 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="2:8" ht="246" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
@@ -587,19 +656,21 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -608,49 +679,86 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="183" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\Desktop\ehb_vakken\dynamicWeb\Exam\Project-Dynamic-Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="11_F25DC773A252ABDACC10483A31DF42745BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FB376B-060F-42BD-B2E3-6F0C548E8E1C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569204C9-D857-4574-B249-9033F4B542D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
   </si>
   <si>
-    <t>Sorteermethode…</t>
-  </si>
-  <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>Groepsleden: Lilian Levano, Bilal Benhammou</t>
+  </si>
+  <si>
+    <t>Voeg een sorteermethode toe die de lijst met culturele locaties alfabetisch sorteert op basis van de naam (nl of fr).                                                                            De sortering moet de taal uit de localStorage lezen. Plaats de sorteerlogica direct na het toekennen van de ID's aan de locaties, zodat de initiële lijst gesorteerd wordt getoond.                                                     Herhaal dezelfde sorteerlogica in de event listener van de taalknoppen, zodat de lijst opnieuw wordt gesorteerd telkens de gebruiker van taal verandert.  Op deze manier blijft de weergave altijd consistent en gebruiksvriendelijk.</t>
   </si>
 </sst>
 </file>
@@ -270,10 +270,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,7 +546,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="63" x14ac:dyDescent="0.25">
@@ -590,10 +586,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -613,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -636,10 +632,10 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -659,10 +655,10 @@
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -679,13 +675,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -702,13 +698,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -731,7 +727,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
@@ -748,13 +744,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\Desktop\ehb_vakken\dynamicWeb\Exam\Project-Dynamic-Web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569204C9-D857-4574-B249-9033F4B542D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{569204C9-D857-4574-B249-9033F4B542D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B0F070-77B2-4D06-A77B-A6FAAF4A9A61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,9 +80,6 @@
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om een specifieke locatie op te zoeken, zodat ik op een snelle manier een locatie kan vinden.</t>
   </si>
   <si>
-    <t>Als een user die de website bezoekt, wil ik de mogelijkheid hebben om de lijst op de homepage te sorteren, zodat ik de locaties kan zien in de volgorde dat ik wil.</t>
-  </si>
-  <si>
     <t>Als een user die de website bezoekt, wil ik de mogelijkheid om bepaalde voorkeuren (bijvoorbeeld: mijn taal) te veranderen en die op te slagen doorheen verschillende sessies.</t>
   </si>
   <si>
@@ -113,12 +110,6 @@
 Bij geen resultaten wordt een melding weergegeven</t>
   </si>
   <si>
-    <t xml:space="preserve">De gebruiker kan de lijst sorteren volgens minstens één criterium
-De sortering wordt correct toegepast op de volledige lijst
-De lijst wordt visueel aangepast na sortering
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">De gebruiker kan locaties toevoegen aan favorieten
 Favorieten worden opgeslagen in LocalStorage
 Favorieten blijven bewaard tussen sessies
@@ -173,6 +164,15 @@
   </si>
   <si>
     <t>Voeg een sorteermethode toe die de lijst met culturele locaties alfabetisch sorteert op basis van de naam (nl of fr).                                                                            De sortering moet de taal uit de localStorage lezen. Plaats de sorteerlogica direct na het toekennen van de ID's aan de locaties, zodat de initiële lijst gesorteerd wordt getoond.                                                     Herhaal dezelfde sorteerlogica in de event listener van de taalknoppen, zodat de lijst opnieuw wordt gesorteerd telkens de gebruiker van taal verandert.  Op deze manier blijft de weergave altijd consistent en gebruiksvriendelijk.</t>
+  </si>
+  <si>
+    <t>Als een user die de website bezoekt, wil ik de verschillende locaties op alfabetisch volgorde gesorteerd zien, op basis van taal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De verschillende locaties worden op alfabetische volgorde gesorteerd
+De sortering wordt correct toegepast op de volledige lijst
+De lijst wordt visueel aangepast na sortering
+</t>
   </si>
 </sst>
 </file>
@@ -270,6 +270,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -546,7 +550,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="63" x14ac:dyDescent="0.25">
@@ -586,10 +590,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -609,10 +613,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -632,10 +636,10 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -652,13 +656,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -675,13 +679,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -698,13 +702,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -727,7 +731,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
@@ -744,13 +748,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>

--- a/backlog project.xlsx
+++ b/backlog project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehb-my.sharepoint.com/personal/lilian_levano_student_ehb_be/Documents/école ehb/cours/dynamic web prg1 s2/ExamenProject/Project-Dynamic-Web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{569204C9-D857-4574-B249-9033F4B542D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B0F070-77B2-4D06-A77B-A6FAAF4A9A61}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{569204C9-D857-4574-B249-9033F4B542D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFB3B6C2-67C0-4CAE-9346-0D9BD762F595}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -761,7 +761,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>